--- a/cond.xlsx
+++ b/cond.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27820" windowHeight="12760" activeTab="1"/>
+    <workbookView windowWidth="27820" windowHeight="11800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="category" sheetId="1" r:id="rId1"/>
@@ -99,12 +99,12 @@
     <t>discount_percent</t>
   </si>
   <si>
+    <t>Классический торт</t>
+  </si>
+  <si>
     <t>Торт</t>
   </si>
   <si>
-    <t>Классический торт</t>
-  </si>
-  <si>
     <t>1200.00</t>
   </si>
   <si>
@@ -174,12 +174,12 @@
     <t>420.00</t>
   </si>
   <si>
+    <t>Заварное пирожное</t>
+  </si>
+  <si>
     <t>Пирожное</t>
   </si>
   <si>
-    <t>Заварное пирожное</t>
-  </si>
-  <si>
     <t>150.00</t>
   </si>
   <si>
@@ -201,21 +201,21 @@
     <t>160.00</t>
   </si>
   <si>
+    <t>Сдобная булка с корицей</t>
+  </si>
+  <si>
     <t>Булочка</t>
   </si>
   <si>
-    <t>Сдобная булка с корицей</t>
-  </si>
-  <si>
     <t>110.00</t>
   </si>
   <si>
+    <t>Миндальный круассан</t>
+  </si>
+  <si>
     <t>Круассан</t>
   </si>
   <si>
-    <t>Миндальный круассан</t>
-  </si>
-  <si>
     <t>190.00</t>
   </si>
   <si>
@@ -225,82 +225,82 @@
     <t>140.00</t>
   </si>
   <si>
+    <t>Улитка с изюмом и кремом</t>
+  </si>
+  <si>
     <t>Улитка</t>
   </si>
   <si>
-    <t>Улитка с изюмом и кремом</t>
-  </si>
-  <si>
     <t>130.00</t>
   </si>
   <si>
+    <t>Клубничный трайфл в стакане</t>
+  </si>
+  <si>
     <t>Трайфл</t>
   </si>
   <si>
-    <t>Клубничный трайфл в стакане</t>
-  </si>
-  <si>
     <t>Шоколадный трайфл</t>
   </si>
   <si>
+    <t>Сливочная панна-котта</t>
+  </si>
+  <si>
     <t>Панна-котта</t>
   </si>
   <si>
-    <t>Сливочная панна-котта</t>
-  </si>
-  <si>
     <t>220.00</t>
   </si>
   <si>
+    <t>Ягодный мусс</t>
+  </si>
+  <si>
     <t>Мусс</t>
   </si>
   <si>
-    <t>Ягодный мусс</t>
-  </si>
-  <si>
     <t>240.00</t>
   </si>
   <si>
+    <t>Кофе Капучино 300мл</t>
+  </si>
+  <si>
     <t>Кофе</t>
   </si>
   <si>
-    <t>Кофе Капучино 300мл</t>
-  </si>
-  <si>
     <t>Кофе Латте 400мл</t>
   </si>
   <si>
     <t>210.00</t>
   </si>
   <si>
+    <t>Авторский облепиховый чай</t>
+  </si>
+  <si>
     <t>Чай</t>
   </si>
   <si>
-    <t>Авторский облепиховый чай</t>
+    <t>Цитрусовый лимонад</t>
   </si>
   <si>
     <t>Лимонад</t>
   </si>
   <si>
-    <t>Цитрусовый лимонад</t>
-  </si>
-  <si>
     <t>170.00</t>
   </si>
   <si>
+    <t>Подарочный бокс Сладкий</t>
+  </si>
+  <si>
     <t>Бокс #1</t>
   </si>
   <si>
-    <t>Подарочный бокс Сладкий</t>
-  </si>
-  <si>
     <t>1500.00</t>
   </si>
   <si>
+    <t>Подарочный бокс Премиум</t>
+  </si>
+  <si>
     <t>Бокс #2</t>
-  </si>
-  <si>
-    <t>Подарочный бокс Премиум</t>
   </si>
   <si>
     <t>2500.00</t>
@@ -1553,7 +1553,6 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="32.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="24.0982142857143" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1599,13 +1598,13 @@
     </row>
     <row r="3" customHeight="1" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>27</v>
@@ -1619,13 +1618,13 @@
     </row>
     <row r="4" customHeight="1" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>29</v>
@@ -1639,13 +1638,13 @@
     </row>
     <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>31</v>
@@ -1659,13 +1658,13 @@
     </row>
     <row r="6" customHeight="1" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
@@ -1679,13 +1678,13 @@
     </row>
     <row r="7" customHeight="1" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>35</v>
@@ -1699,13 +1698,13 @@
     </row>
     <row r="8" customHeight="1" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>37</v>
@@ -1719,13 +1718,13 @@
     </row>
     <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>39</v>
@@ -1739,13 +1738,13 @@
     </row>
     <row r="10" customHeight="1" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>41</v>
@@ -1759,13 +1758,13 @@
     </row>
     <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>43</v>
@@ -1779,13 +1778,13 @@
     </row>
     <row r="12" customHeight="1" spans="1:6">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>45</v>
@@ -1799,13 +1798,13 @@
     </row>
     <row r="13" customHeight="1" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>47</v>
@@ -1839,13 +1838,13 @@
     </row>
     <row r="15" customHeight="1" spans="1:6">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>52</v>
@@ -1859,13 +1858,13 @@
     </row>
     <row r="16" customHeight="1" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>54</v>
@@ -1879,13 +1878,13 @@
     </row>
     <row r="17" customHeight="1" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>56</v>
@@ -1939,13 +1938,13 @@
     </row>
     <row r="20" customHeight="1" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>64</v>
@@ -1999,13 +1998,13 @@
     </row>
     <row r="23" customHeight="1" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>33</v>
@@ -2079,13 +2078,13 @@
     </row>
     <row r="27" customHeight="1" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>80</v>
